--- a/publication/results/tables/table3_master_benchmark_vaers.xlsx
+++ b/publication/results/tables/table3_master_benchmark_vaers.xlsx
@@ -686,32 +686,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.2949</t>
+          <t>0.3418</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.1973</t>
+          <t>0.2368</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.2364</t>
+          <t>0.2797</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.6448</t>
+          <t>0.6714</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.3780</t>
+          <t>0.4129</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.4766</t>
+          <t>0.5113</t>
         </is>
       </c>
     </row>

--- a/publication/results/tables/table3_master_benchmark_vaers.xlsx
+++ b/publication/results/tables/table3_master_benchmark_vaers.xlsx
@@ -597,27 +597,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.6268 +- 0.0203</t>
+          <t>0.7076 +- 0.0164</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.6594 +- 0.0196</t>
+          <t>0.7015 +- 0.0174</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.8619 +- 0.0095</t>
+          <t>0.8618 +- 0.0096</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.7205 +- 0.0153</t>
+          <t>0.8135 +- 0.0119</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.7848 +- 0.0127</t>
+          <t>0.8370 +- 0.0095</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.6324 +- 0.0183</t>
+          <t>0.7132 +- 0.0157</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.6595 +- 0.0177</t>
+          <t>0.7009 +- 0.0163</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7279 +- 0.0139</t>
+          <t>0.8209 +- 0.0118</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.7882 +- 0.0112</t>
+          <t>0.8397 +- 0.0089</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LLaMA 4 (1-shot, Target Filtered)</t>
+          <t>LLaMA 4 (1-shot, Tagged)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -686,32 +686,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.3418</t>
+          <t>0.3378</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.2368</t>
+          <t>0.3388</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.2797</t>
+          <t>0.3383</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.6714</t>
+          <t>0.6691</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4129</t>
+          <t>0.6134</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.5113</t>
+          <t>0.6400</t>
         </is>
       </c>
     </row>
